--- a/Översikt HEBY.xlsx
+++ b/Översikt HEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45425</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45944</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45729</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45123</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45946</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>45618</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45777</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>46155</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45777</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>44914</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>46149</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>46149</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44914</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>45240</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45117</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>46254</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45687</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>44585</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>44573</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>46070</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>45014</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45485</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>45222</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45124</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44788</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45112</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44847</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44524</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>46163</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>46217</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>46282</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45573</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45618</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45485</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45964</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45313</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45898</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>45944</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>45170</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>45992</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>46140</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>46177</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45278</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>45419</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>45460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45373</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>44847</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>44509</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44826</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45083</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>45093</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>46070</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>46071</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>45411</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>46084</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>46085</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>45723</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>46140</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45317</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45098</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>45355</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45117</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>45972</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>46072</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45469</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45883</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45231</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>45278</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>46231</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>45050</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>45617</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>45208</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45770</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44501</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>45622</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45418</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44629</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45548</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>46107</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>44886</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>44620</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>44477</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44754</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44615</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44466</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>44516</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44511</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>44586</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44585</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44757</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>44508</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44509</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44756</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44578</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>44480</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44788</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>44852</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>44508</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>44505</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>44517</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>44516</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44565</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>44844</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>44712</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>44832</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>44550</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>44509</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>44735</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>44743</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>44519</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44850</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>44614</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>44491</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>44725</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>44522</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>44832</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44748</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>44551</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>44685</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>44769</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>44650</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44655</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44722</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>44700</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>44532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>44573</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>44753</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45370</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45379</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45331</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45687</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>45688</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45342</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45231</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45390</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>45250</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>45308</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>44865</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45243</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>44849</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>44823</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45250</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45231</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>44833</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>44978</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>45175</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>44984</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44984</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>44925</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>46023</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>44886</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>44946</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45328</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45133</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44531</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45339</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>45502</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45112</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45209</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45610</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>44477</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45797</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44844</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>44978</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>45889</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44574</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45439</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45891</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44512</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45547</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>46044</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45898</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>45898</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>44913</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45075</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>46045</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>46048</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>44586</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>46052</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>46052</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>46051</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>46052</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>45804</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>46084</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>46056</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45566</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44903</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>46058</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45912</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45804</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>46058</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>46057</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>46057</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>46058</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>45106</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>45294</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45092</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45092</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>46059</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45803</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>44574</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46063</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>46063</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45922</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45519</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45922</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45922</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45705</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45119</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>46071</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>46056</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>44945</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>46073</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>46073</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>46076</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44873</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>46058</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45567</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>46079</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45331</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45062</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45050</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44943</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>44944</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>44944</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45390</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45398</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45680</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44984</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45519</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45089</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45586</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44974</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45930</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44943</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45628</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45708</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>45596</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>46093</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>46093</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>46093</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44916</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>46093</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45364</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45364</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>46094</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45943</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45944</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45945</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>44888</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>46101</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45006</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45058</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44701</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45950</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>45952</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45952</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45951</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>44601</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>46110</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45422</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>44697</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45957</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45958</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>46112</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>46112</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>46112</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>46112</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>46112</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>46114</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>44491</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>46114</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45092</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45113</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>44956</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44960</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45966</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>46127</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>44984</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44533</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45967</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>45971</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>45971</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45972</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>46126</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>46126</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>45294</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>45818</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>45980</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>46133</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45980</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45980</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>44802</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45818</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46135</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>46135</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>45951</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45749</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45895</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45058</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45992</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45030</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>45895</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>44810</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44984</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45114</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>44754</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45132</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45132</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44694</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>45132</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45818</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45317</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>45932</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>46140</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>46140</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>46140</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>44609</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45098</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>46003</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>46003</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>46005</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45411</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>46003</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>46140</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45946</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>46007</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45884</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>46140</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>45932</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>45820</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>45743</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>45884</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>45351</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>45218</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>45218</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>45891</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45946</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45904</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45825</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>45216</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>45826</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>46140</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>44684</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>45805</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44939</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>46141</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>45827</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>45827</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>45832</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>44538</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>45099</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>45670</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>46149</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>44944</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44917</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>45764</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>44862</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44568</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45805</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45764</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45770</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>45279</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45321</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>46160</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>45090</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>45838</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>44517</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45103</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45761</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>44543</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>44914</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>45845</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45825</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>46164</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>46163</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45847</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45117</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>45117</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45117</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>46167</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>45852</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>45852</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45317</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>46168</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>44552</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>46169</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>46037</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32863,7 +32863,7 @@
         <v>45967</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45006</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>46174</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45029</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>44568</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>45098</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44974</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45532</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45373</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>46178</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>46178</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>45726</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45166</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>44993</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>45511</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>44511</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>45117</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>45589</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44620</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34323,7 +34323,7 @@
         <v>44951</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>44613</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>45331</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>44558</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>45173</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>45173</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>45008</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34834,7 +34834,7 @@
         <v>46198</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34912,7 +34912,7 @@
         <v>45547</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>46198</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>46072</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>45929</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>45337</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>45181</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45599</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>45103</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>45727</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35579,7 +35579,7 @@
         <v>45777</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35652,7 +35652,7 @@
         <v>45747</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>45884</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
         <v>45883</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>46205</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>45674</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44802</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44802</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>46205</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>45166</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>46205</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>46252</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>44623</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>45050</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>44609</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>46253</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>46254</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>45195</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>46254</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>46254</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>46255</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45195</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45133</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>44697</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>44841</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>46255</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>46255</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>46255</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>46255</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>46255</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>45138</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>46255</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>46255</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>46258</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>46258</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>44694</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>46253</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>46258</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44788</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45243</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>46262</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>45250</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>44752</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>46220</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38861,7 +38861,7 @@
         <v>45175</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>44791</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39007,7 +39007,7 @@
         <v>45181</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39080,7 +39080,7 @@
         <v>44734</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>46223</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>46265</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>46223</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>46224</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>45317</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44734</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>46268</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>46268</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44753</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
         <v>46272</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>46272</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>46272</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>46269</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>46231</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>46231</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>46273</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>46272</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>45118</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45293</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>45693</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>44781</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>46237</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>46280</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>45128</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>46280</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>46280</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41111,7 +41111,7 @@
         <v>46237</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>46237</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>45197</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>46279</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>46278</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>46279</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41554,7 +41554,7 @@
         <v>46281</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>44732</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>46238</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>46238</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45582</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>44914</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>45406</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>46119</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44911</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>44694</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
         <v>44978</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>46280</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>46286</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>44495</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>46281</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>45572</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>44659</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>46287</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>44614</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>45453</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>44942</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44942</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>46289</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43253,7 +43253,7 @@
         <v>46289</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>46290</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>45664</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43477,7 +43477,7 @@
         <v>44602</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45113</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>46289</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>44684</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>44522</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>46289</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>46289</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>44753</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>45006</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>44734</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>46289</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44300,7 +44300,7 @@
         <v>46289</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>45083</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44446,7 +44446,7 @@
         <v>44964</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44519,7 +44519,7 @@
         <v>44701</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44592,7 +44592,7 @@
         <v>45013</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>44480</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44738,7 +44738,7 @@
         <v>44984</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44811,7 +44811,7 @@
         <v>45215</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>44984</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>44644</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45035</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>45639</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45176,7 +45176,7 @@
         <v>44981</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>44914</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45322,7 +45322,7 @@
         <v>45376</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>45252</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>45111</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45135</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>45132</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45117</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>45607</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45599</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45344</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45994,7 +45994,7 @@
         <v>45686</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>44911</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45551</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>45519</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>45519</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>44900</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46432,7 +46432,7 @@
         <v>45058</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45209</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44979</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45713</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45321</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>44875</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45117</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45740</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45175</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>45617</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>45747</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>45786</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47318,7 +47318,7 @@
         <v>45394</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>45786</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45355</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>45390</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>44644</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>45786</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45786</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>44629</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47917,7 +47917,7 @@
         <v>44546</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
         <v>44588</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>44684</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>44629</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45191</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>44788</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>45590</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>45411</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45485</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48619,7 +48619,7 @@
         <v>45699</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>45411</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>44788</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48843,7 +48843,7 @@
         <v>45987</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48916,7 +48916,7 @@
         <v>46000</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>46085</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>46190</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>46273</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>

--- a/Översikt HEBY.xlsx
+++ b/Översikt HEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45425</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45944</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45729</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45123</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45946</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>45618</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45777</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>46155</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45777</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>44914</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>46149</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>46149</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44914</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>45240</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45117</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>46254</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>45687</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>44585</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>44573</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>46070</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>45014</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45485</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>44840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>45222</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45124</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44788</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45112</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44847</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44524</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>46163</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>46217</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>46282</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45573</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>45618</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45485</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45964</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45313</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45898</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>45944</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>45170</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         <v>45992</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>46140</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>46177</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45278</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>45419</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>45460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45373</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>44847</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>44509</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44826</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45083</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>45093</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>46070</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>46071</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>45411</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>46084</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>46085</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>45723</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>46140</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45317</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45098</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>45355</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45117</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>45972</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>46072</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>45469</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45883</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45231</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>45278</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>46231</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>45050</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>45617</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>45208</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45770</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>44501</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>45622</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>45418</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>44629</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45548</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>46107</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44756</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>44886</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>44620</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>44477</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44754</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44615</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44466</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>44516</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44511</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>44586</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44585</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44757</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>44508</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44509</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44756</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44578</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>44480</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44788</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>44852</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>44508</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>44505</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>44517</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>44516</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44565</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>44844</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>44712</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>44832</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>44550</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>44509</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>44735</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>44743</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>44519</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44850</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>44614</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>44491</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>44725</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>44522</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>44832</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44748</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>44551</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>44685</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>44769</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>44650</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44655</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44722</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>44700</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>44532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>44573</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>44753</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>44614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45370</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45379</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>45331</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45687</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>45688</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45342</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45231</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>45390</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14134,7 +14134,7 @@
         <v>45250</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>45308</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>44865</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45243</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>44849</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>44823</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>45250</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45231</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>44833</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>44978</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>45175</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>44984</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>44984</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>44925</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>46023</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>44886</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>44946</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>45328</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>45133</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15531,7 +15531,7 @@
         <v>44531</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45339</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>45502</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45112</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45209</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45610</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>44477</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45797</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>44844</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>44978</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>45889</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44574</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45439</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45891</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>44512</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45547</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>46044</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45898</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>45898</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>44913</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45075</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>46045</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>46048</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>44586</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>46052</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>46052</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>46051</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>46052</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17605,7 +17605,7 @@
         <v>45804</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>46084</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17751,7 +17751,7 @@
         <v>46056</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45566</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>44903</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>46058</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45912</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45804</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>46058</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>46057</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>46057</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>46058</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>45106</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>45294</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>45092</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
         <v>45092</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>46059</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45803</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>44574</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>46063</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>46063</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19148,7 +19148,7 @@
         <v>45922</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
         <v>45519</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45922</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45922</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45705</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45119</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>46071</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>46056</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>44945</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>46073</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>46073</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>46076</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44873</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>46058</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45567</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>46079</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45331</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45062</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45050</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44943</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>44944</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>44944</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45390</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45398</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45680</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44984</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45519</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45089</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45586</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44974</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45930</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>44943</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21499,7 +21499,7 @@
         <v>45628</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>45708</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21645,7 +21645,7 @@
         <v>45596</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21718,7 +21718,7 @@
         <v>46093</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>46093</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>46093</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>44916</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>46093</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45364</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45364</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>46094</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>45943</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45944</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45945</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>44888</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>46101</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45006</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45058</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44701</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45950</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>45952</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45952</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45951</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>44601</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>46110</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45422</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>44697</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23495,7 +23495,7 @@
         <v>45957</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>45958</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23641,7 +23641,7 @@
         <v>46112</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>46112</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>46112</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>46112</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>46112</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>46114</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>44491</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>46114</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45092</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45113</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>44956</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44960</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45966</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>46127</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>44984</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>44533</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>45967</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>45971</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>45971</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45972</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>46126</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>46126</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25257,7 +25257,7 @@
         <v>45294</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>45818</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>45980</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>46133</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45980</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45980</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>44802</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>45818</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>46135</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>46135</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>45951</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45749</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45895</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45058</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45992</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45030</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>45895</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>44810</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>44984</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45114</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>44754</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45132</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45132</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44694</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>45132</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45818</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45317</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>45932</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>46140</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>46140</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>46140</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>44609</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45098</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>46003</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>46003</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>46005</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45411</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>46003</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>46140</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45946</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>46007</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>45884</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>46140</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28481,7 +28481,7 @@
         <v>45932</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>45820</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>45743</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>45884</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>45351</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>45218</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>45218</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>45891</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45946</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45904</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45825</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>45216</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>45826</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>46140</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>44684</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>45805</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44939</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>46141</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>45827</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29893,7 +29893,7 @@
         <v>45827</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29971,7 +29971,7 @@
         <v>45832</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30044,7 +30044,7 @@
         <v>44538</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30117,7 +30117,7 @@
         <v>45099</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>45670</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>46149</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>44944</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>44917</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30487,7 +30487,7 @@
         <v>45764</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30565,7 +30565,7 @@
         <v>44862</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44568</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45805</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30784,7 +30784,7 @@
         <v>45764</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45770</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>45279</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45321</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>46160</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>45090</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31232,7 +31232,7 @@
         <v>45838</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31305,7 +31305,7 @@
         <v>44517</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31383,7 +31383,7 @@
         <v>45103</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>45761</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>44543</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>44914</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>45845</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>45825</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>46164</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>46163</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31982,7 +31982,7 @@
         <v>45847</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45117</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>45117</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45117</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>46167</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>45852</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>45852</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>45317</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>46168</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>44552</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>46169</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32790,7 +32790,7 @@
         <v>46037</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32863,7 +32863,7 @@
         <v>45967</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45006</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>46174</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>46174</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45029</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>44568</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33301,7 +33301,7 @@
         <v>45098</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44974</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45532</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45373</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33593,7 +33593,7 @@
         <v>46178</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>46178</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33739,7 +33739,7 @@
         <v>45726</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>45166</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>44993</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>45511</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>44511</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>45117</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>45589</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>44620</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34323,7 +34323,7 @@
         <v>44951</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>44613</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>45331</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>44558</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>45173</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>45173</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>45008</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34834,7 +34834,7 @@
         <v>46198</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34912,7 +34912,7 @@
         <v>45547</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         <v>46198</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35063,7 +35063,7 @@
         <v>46072</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35136,7 +35136,7 @@
         <v>45929</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>45337</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>45181</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35355,7 +35355,7 @@
         <v>45599</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>45103</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>45727</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35579,7 +35579,7 @@
         <v>45777</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35652,7 +35652,7 @@
         <v>45747</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>45884</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
         <v>45883</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>46205</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>45674</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>44802</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36100,7 +36100,7 @@
         <v>44802</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36173,7 +36173,7 @@
         <v>46205</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>45166</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>46205</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>46252</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36475,7 +36475,7 @@
         <v>44623</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>45050</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>44609</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>46253</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>46254</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36855,7 +36855,7 @@
         <v>45195</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>46254</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37006,7 +37006,7 @@
         <v>46254</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37084,7 +37084,7 @@
         <v>46255</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>45195</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37230,7 +37230,7 @@
         <v>45133</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>44697</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>44841</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37449,7 +37449,7 @@
         <v>46255</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37522,7 +37522,7 @@
         <v>46255</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>46255</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>46255</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>46255</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37824,7 +37824,7 @@
         <v>45138</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37897,7 +37897,7 @@
         <v>46255</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37975,7 +37975,7 @@
         <v>46255</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>46258</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38121,7 +38121,7 @@
         <v>46258</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>44694</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>46253</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>46258</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44788</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38491,7 +38491,7 @@
         <v>45243</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
         <v>46262</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>45250</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>44752</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38783,7 +38783,7 @@
         <v>46220</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38861,7 +38861,7 @@
         <v>45175</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38934,7 +38934,7 @@
         <v>44791</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39007,7 +39007,7 @@
         <v>45181</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39080,7 +39080,7 @@
         <v>44734</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>46223</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39231,7 +39231,7 @@
         <v>46265</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39304,7 +39304,7 @@
         <v>46223</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>46224</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>45317</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44734</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>46268</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39684,7 +39684,7 @@
         <v>46268</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39762,7 +39762,7 @@
         <v>44753</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
         <v>46272</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>46272</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>46272</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40064,7 +40064,7 @@
         <v>46269</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>46231</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>46231</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>46273</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>46272</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40439,7 +40439,7 @@
         <v>45118</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45293</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>45693</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>44781</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>46237</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>46280</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>45128</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>46280</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>46280</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41111,7 +41111,7 @@
         <v>46237</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>46237</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>45197</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>46279</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>46278</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>46279</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41554,7 +41554,7 @@
         <v>46281</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>44732</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>46238</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>46238</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45582</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>44914</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>45406</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>46119</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44911</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>44694</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
         <v>44978</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42372,7 +42372,7 @@
         <v>46280</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>46286</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>44495</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42591,7 +42591,7 @@
         <v>46281</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42664,7 +42664,7 @@
         <v>45572</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>44659</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42810,7 +42810,7 @@
         <v>46287</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>44614</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>45453</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43029,7 +43029,7 @@
         <v>44942</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44942</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>46289</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43253,7 +43253,7 @@
         <v>46289</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>46290</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>45664</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43477,7 +43477,7 @@
         <v>44602</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43550,7 +43550,7 @@
         <v>45113</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43623,7 +43623,7 @@
         <v>46289</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>44684</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>44522</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43852,7 +43852,7 @@
         <v>46289</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>46289</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44003,7 +44003,7 @@
         <v>44753</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>45006</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>44734</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>46289</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44300,7 +44300,7 @@
         <v>46289</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>45083</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44446,7 +44446,7 @@
         <v>44964</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44519,7 +44519,7 @@
         <v>44701</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44592,7 +44592,7 @@
         <v>45013</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44665,7 +44665,7 @@
         <v>44480</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44738,7 +44738,7 @@
         <v>44984</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44811,7 +44811,7 @@
         <v>45215</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>44984</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44957,7 +44957,7 @@
         <v>44644</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45035</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>45639</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45176,7 +45176,7 @@
         <v>44981</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45249,7 +45249,7 @@
         <v>44914</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45322,7 +45322,7 @@
         <v>45376</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>45252</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>45111</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45135</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>45132</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45117</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>45607</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45599</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>45344</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45994,7 +45994,7 @@
         <v>45686</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>44911</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45551</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>45519</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>45519</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>44900</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46432,7 +46432,7 @@
         <v>45058</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45209</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44979</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45713</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45321</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>44875</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45117</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45740</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45175</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>45617</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>45747</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>45786</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47318,7 +47318,7 @@
         <v>45394</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>45786</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45355</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>45390</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>44644</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>45786</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45786</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>44629</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47917,7 +47917,7 @@
         <v>44546</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
         <v>44588</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>44684</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>44629</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45191</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>44788</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>45590</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>45411</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45485</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48619,7 +48619,7 @@
         <v>45699</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>45411</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>44788</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48843,7 +48843,7 @@
         <v>45987</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48916,7 +48916,7 @@
         <v>46000</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>46085</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>46190</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49145,7 +49145,7 @@
         <v>46273</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>

--- a/Översikt HEBY.xlsx
+++ b/Översikt HEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45425</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45944</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45729</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45123</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45946</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>45618</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45777</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>46155</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45777</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>44914</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>46149</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44914</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45687</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45117</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>46254</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>44585</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>44573</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>45124</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>46070</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>45014</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>44840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45222</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>45485</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44788</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45112</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44847</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44524</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45618</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>46163</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>46217</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>46282</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45573</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45485</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45964</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45313</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45898</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>45944</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>45992</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>45170</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45278</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>46140</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>46177</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>45419</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>45460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45373</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>44847</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>44509</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44826</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45093</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45770</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45411</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>46071</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>46070</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>46084</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>46085</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>45083</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>45317</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>45723</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>45622</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>46140</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45418</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>45050</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>45617</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45883</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>46072</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>45972</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>44501</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>45098</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45355</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>46231</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45117</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>45469</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>45231</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>45208</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>46295</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>45278</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45548</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44629</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>46107</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44756</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44886</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44620</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44754</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44615</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>44516</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44511</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44586</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>44585</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44757</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>44508</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>44509</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44756</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44578</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>44480</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44788</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44852</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>44508</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44505</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44517</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44516</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>44565</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44844</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>44712</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44550</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44832</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44509</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>44735</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44743</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44519</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>44850</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44614</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>44491</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44725</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>44522</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>44832</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>44748</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>44551</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>44685</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44769</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>44650</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>44655</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>44722</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>44700</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44573</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44753</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>44942</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44609</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44841</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45231</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>44802</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>44552</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>45133</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44732</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45599</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44697</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>45390</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>45786</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45786</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>44849</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>45786</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45786</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45670</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>44694</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>46003</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>46003</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>44960</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>46003</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45761</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>44844</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44914</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>45035</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45749</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>46005</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>46007</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>44865</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45884</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45688</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45215</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45889</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44543</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>44788</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>46023</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45891</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>44810</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45331</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44684</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45898</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44684</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45898</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>44734</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>44875</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44946</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45328</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45133</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45209</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>44522</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>46045</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45112</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45797</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45175</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45610</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>46044</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45912</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>44477</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>45111</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>45294</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>46048</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>45547</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>45106</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>44862</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45092</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>45092</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45803</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45705</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>46051</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>45804</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>45804</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>45390</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>46052</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>45708</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45922</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>44984</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>46052</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>45922</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45922</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>46084</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>44913</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>46052</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>45293</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>46056</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>46057</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>46057</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>46058</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45519</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45439</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>46058</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>46059</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>46058</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45628</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>46063</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>46063</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45547</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>45930</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>44574</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45680</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>44984</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45321</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>46056</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>46071</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>46073</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>46073</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44886</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45596</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45398</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>46076</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45944</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45519</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>46058</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45279</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45945</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45687</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>45089</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>44917</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45950</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>46079</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45951</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45952</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45952</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>45058</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>45453</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45957</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44984</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45958</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45502</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45006</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>46094</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44609</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45567</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>45967</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>46093</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>46093</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>46093</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45966</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>46093</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>44914</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45218</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45971</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45971</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45972</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>44781</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44984</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>44984</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>46101</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44623</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45818</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44601</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>45818</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>45980</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45980</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45980</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>46110</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>46112</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>46112</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>46112</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>46112</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>46112</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45820</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>46114</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45339</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45331</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45331</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>46114</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45317</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45895</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>45951</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45617</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>44614</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45825</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45519</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45519</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>45586</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44701</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>45992</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>46126</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>45826</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44984</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>46126</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>45827</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>45119</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>45132</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>45342</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>46127</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>46133</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45764</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>45764</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45607</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>46135</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>46135</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45832</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45674</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44533</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45098</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45904</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44754</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>45838</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45884</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>44697</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>44900</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>44701</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45932</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>45006</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>45317</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>45825</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>45847</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>45308</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>45891</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45845</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>44833</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44978</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>45946</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>45852</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45932</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>44568</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45852</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45113</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>44939</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45818</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>45946</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45321</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>44734</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45411</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45884</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45364</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>45090</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>44480</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45058</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45390</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>45895</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45181</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>46140</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>46140</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>45351</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>46141</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>46140</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>46140</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45114</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45805</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>46140</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>46140</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44694</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45209</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>45197</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>45175</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>46149</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45740</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45805</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45770</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45218</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45250</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>44531</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44511</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45551</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45029</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>46160</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>45406</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45599</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>46163</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>44568</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>46164</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>46037</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>46169</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>45967</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>46168</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>46174</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>45128</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>46174</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>44644</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>44942</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>45013</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45777</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45883</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>45092</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>46178</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>46178</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>44659</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>44694</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45639</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45337</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>45589</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45181</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>45062</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>45135</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45364</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>46198</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>46198</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44512</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>46072</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>44903</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>45929</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>44802</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         <v>44802</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44734</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>44517</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>44558</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>45250</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>46205</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>46205</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>46205</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>45243</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>44791</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44945</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>46258</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>46258</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45117</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>44974</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>46258</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>45113</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36803,7 +36803,7 @@
         <v>45132</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45132</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45132</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>45050</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44944</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>46262</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45566</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>46265</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>46220</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>46223</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>46223</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>45030</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>45006</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45117</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>44964</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>45195</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>46224</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>46269</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>46268</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>46268</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45138</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>46272</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38444,7 +38444,7 @@
         <v>46273</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>46272</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>46272</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>46272</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>45166</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45373</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>45216</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>46231</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>46231</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>46279</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>46279</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>46278</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>46238</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>46237</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>46238</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>46237</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>46237</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45103</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>46280</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>46280</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>46280</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>46281</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45376</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40173,7 +40173,7 @@
         <v>45083</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>44944</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         <v>45379</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>44574</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>45243</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>44586</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>44491</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>44911</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40757,7 +40757,7 @@
         <v>46119</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>46280</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>45317</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>44979</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45098</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41122,7 +41122,7 @@
         <v>46287</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>46281</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>46289</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>46286</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44888</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41497,7 +41497,7 @@
         <v>46289</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>46289</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>46289</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>44978</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>46289</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>46289</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>46289</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>45294</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>45726</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>46293</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42257,7 +42257,7 @@
         <v>46167</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>45532</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>46290</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45166</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>44984</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>44943</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>44943</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42768,7 +42768,7 @@
         <v>44944</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42841,7 +42841,7 @@
         <v>45252</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42919,7 +42919,7 @@
         <v>46293</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>44495</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43070,7 +43070,7 @@
         <v>44914</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>44974</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>46253</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43294,7 +43294,7 @@
         <v>46295</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45173</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>45173</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>46295</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>44956</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>46252</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>45747</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45344</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>46297</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>46296</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>44752</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>45693</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>46254</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>46296</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>46255</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>46255</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>45008</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44570,7 +44570,7 @@
         <v>46254</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>46255</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>46255</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>44602</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>46296</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44950,7 +44950,7 @@
         <v>46296</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>45050</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>46254</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>44911</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>46296</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>46255</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>46255</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>46255</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>44978</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>46253</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>46255</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45778,7 +45778,7 @@
         <v>46296</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45743</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45929,7 +45929,7 @@
         <v>45664</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>45422</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46075,7 +46075,7 @@
         <v>45099</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45231</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>45511</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45058</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>44993</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45572</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>44823</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46596,7 +46596,7 @@
         <v>44753</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45118</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>45582</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>44951</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>45195</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>44916</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>44753</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>44613</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>45075</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>44873</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47331,7 +47331,7 @@
         <v>45175</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>45713</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>44981</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>45117</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45117</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47696,7 +47696,7 @@
         <v>45117</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47769,7 +47769,7 @@
         <v>45250</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>44925</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>45727</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47988,7 +47988,7 @@
         <v>45103</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48061,7 +48061,7 @@
         <v>44620</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45747</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>45394</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>44644</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>45355</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>44629</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48499,7 +48499,7 @@
         <v>44546</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48577,7 +48577,7 @@
         <v>45191</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>44588</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48733,7 +48733,7 @@
         <v>44788</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>44684</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48879,7 +48879,7 @@
         <v>45590</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48957,7 +48957,7 @@
         <v>45411</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49030,7 +49030,7 @@
         <v>45485</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>45699</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49186,7 +49186,7 @@
         <v>45411</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49259,7 +49259,7 @@
         <v>44788</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>44629</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45987</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>46000</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49571,7 +49571,7 @@
         <v>46085</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>46190</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>46273</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>

--- a/Översikt HEBY.xlsx
+++ b/Översikt HEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45425</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45944</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45729</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45123</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45946</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>45618</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45777</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>46155</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45777</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>44914</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>46149</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>44914</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45687</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>45985</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45117</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>46254</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>44585</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>44573</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>45124</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>46070</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>45014</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>44840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45222</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>45485</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44788</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45112</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44847</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44524</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45618</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>46163</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>46217</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>46282</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45573</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45485</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45964</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45313</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45898</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>45944</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>45992</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>45170</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>45278</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>46140</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>46177</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>45419</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>45460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45373</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>44847</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>44509</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44826</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45093</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45770</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45411</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>46071</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>46070</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>46084</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>46085</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>45083</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>45317</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>45723</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>45622</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>46140</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45418</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>45050</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>45617</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45883</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>46072</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>45972</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>44501</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>45098</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>45355</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>46231</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>45117</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>45469</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>45231</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>45208</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>46295</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>45278</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45548</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44629</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>46107</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44756</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44886</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44620</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44754</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44615</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>44516</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44511</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44586</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>44585</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44757</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>44508</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>44509</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10923,7 +10923,7 @@
         <v>44756</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44578</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>44480</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44788</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44852</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>44508</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44505</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>44517</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44516</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>44565</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44844</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>44712</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44550</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44832</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44509</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>44735</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44743</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>44519</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>44850</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44614</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>44491</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44725</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>44522</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>44832</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>44748</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>44551</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>44685</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44769</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12992,7 +12992,7 @@
         <v>44650</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>44655</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>44722</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>44700</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44573</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44753</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>44942</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44609</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44841</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45231</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>44802</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>44552</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>45133</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44732</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>45599</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44697</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>45390</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>45786</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45786</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>44849</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>45786</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45786</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45670</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>44694</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>46003</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>46003</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>44960</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>46003</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45761</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>44844</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44914</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44538</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>45035</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45749</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>46005</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>46007</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>44865</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45884</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45688</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45215</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45889</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16244,7 +16244,7 @@
         <v>44543</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>44788</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>46023</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45891</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>44810</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45331</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44684</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45898</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44684</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45898</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>44734</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>44875</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44946</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45328</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45133</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>45209</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>44522</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>46045</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45112</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>45797</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45175</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45610</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>46044</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45912</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>44477</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18099,7 +18099,7 @@
         <v>45111</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>45294</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18245,7 +18245,7 @@
         <v>46048</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>45547</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>45106</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>44862</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45092</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>45092</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>45803</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45705</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>46051</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>45804</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>45804</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>45390</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>46052</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>45708</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45922</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>44984</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>46052</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>45922</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45922</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>46084</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>44913</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>46052</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>45293</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>46056</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>46057</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>46057</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>46058</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45519</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>45439</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>46058</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
         <v>46059</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>46058</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45628</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>46063</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>46063</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45547</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>45930</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>44574</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45680</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>44984</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45321</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>46056</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>46071</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>46073</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>46073</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44886</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>45596</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>45398</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>46076</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45944</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45519</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>46058</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>45279</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45945</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>45687</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>45089</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>44917</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45950</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>46079</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45951</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45952</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>45952</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>45058</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>45453</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45957</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44984</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45958</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45502</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45006</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>46094</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44609</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45567</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>45967</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>46093</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>46093</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>46093</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45966</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>46093</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>44914</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>45218</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45971</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>45971</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45972</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>44781</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44984</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>44984</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>46101</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>44623</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45818</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44601</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>45818</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>45980</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45980</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45980</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>46110</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>46112</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>46112</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>46112</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>46112</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>46112</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45820</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25658,7 +25658,7 @@
         <v>46114</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45339</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45331</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45331</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>46114</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45317</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45895</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>45951</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45617</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>44614</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45825</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26471,7 +26471,7 @@
         <v>45519</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45519</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26617,7 +26617,7 @@
         <v>45586</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44701</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>45992</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>46126</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>45826</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44984</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>46126</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>45827</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>45119</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>45132</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>45342</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>46127</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>46133</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45764</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>45764</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>45607</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>46135</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>46135</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45832</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45674</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44533</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45098</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45904</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44754</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>45838</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         <v>45884</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>44697</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28653,7 +28653,7 @@
         <v>44900</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>44701</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45932</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>45006</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>45317</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         <v>45825</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         <v>45847</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>45308</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>45891</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45845</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29393,7 +29393,7 @@
         <v>44833</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29466,7 +29466,7 @@
         <v>44978</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>45946</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>45852</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29690,7 +29690,7 @@
         <v>45932</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>44568</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45852</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>45113</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>44939</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>45818</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>45946</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45321</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>44734</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>45411</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45884</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>45364</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>45090</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>44480</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>45058</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45390</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30873,7 +30873,7 @@
         <v>45895</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45181</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>46140</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>46140</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>45351</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31253,7 +31253,7 @@
         <v>46141</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31326,7 +31326,7 @@
         <v>46140</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>46140</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45114</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31555,7 +31555,7 @@
         <v>45805</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>46140</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>46140</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44694</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45209</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>45197</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32008,7 +32008,7 @@
         <v>45175</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32081,7 +32081,7 @@
         <v>46149</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45740</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45805</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45770</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45218</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45250</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32524,7 +32524,7 @@
         <v>44531</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>44511</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32670,7 +32670,7 @@
         <v>45551</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32743,7 +32743,7 @@
         <v>45029</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>46160</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>45406</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32962,7 +32962,7 @@
         <v>45599</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33040,7 +33040,7 @@
         <v>46163</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>44568</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>46164</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>46037</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>46169</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>45967</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>46168</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>46174</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>45128</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33702,7 +33702,7 @@
         <v>46174</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33775,7 +33775,7 @@
         <v>44644</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>44942</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33921,7 +33921,7 @@
         <v>45013</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33994,7 +33994,7 @@
         <v>45777</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45883</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34140,7 +34140,7 @@
         <v>45092</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>46178</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>46178</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34359,7 +34359,7 @@
         <v>44659</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34432,7 +34432,7 @@
         <v>44694</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34505,7 +34505,7 @@
         <v>45639</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34578,7 +34578,7 @@
         <v>45337</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>45589</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45181</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>45062</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>45135</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45364</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>46198</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>46198</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35172,7 +35172,7 @@
         <v>44512</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>46072</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>44903</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>45929</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35469,7 +35469,7 @@
         <v>44802</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35542,7 +35542,7 @@
         <v>44802</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>44734</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>44517</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>44558</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35839,7 +35839,7 @@
         <v>45250</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35912,7 +35912,7 @@
         <v>46205</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35990,7 +35990,7 @@
         <v>46205</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36068,7 +36068,7 @@
         <v>46205</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36141,7 +36141,7 @@
         <v>45243</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         <v>44791</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36287,7 +36287,7 @@
         <v>44945</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>46258</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>46258</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45117</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36579,7 +36579,7 @@
         <v>44974</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36652,7 +36652,7 @@
         <v>46258</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>45113</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36803,7 +36803,7 @@
         <v>45132</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
         <v>45132</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36949,7 +36949,7 @@
         <v>45132</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>45050</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>44944</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>46262</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45566</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>46265</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>46220</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>46223</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37548,7 +37548,7 @@
         <v>46223</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>45030</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>45006</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45117</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>44964</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>45195</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>46224</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>46269</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>46268</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>46268</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45138</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38371,7 +38371,7 @@
         <v>46272</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38444,7 +38444,7 @@
         <v>46273</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>46272</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>46272</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>46272</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>45166</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45373</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>45216</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>46231</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>46231</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>46279</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>46279</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>46278</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>46238</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>46237</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>46238</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>46237</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>46237</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45103</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>46280</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>46280</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>46280</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>46281</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45376</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40173,7 +40173,7 @@
         <v>45083</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>44944</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         <v>45379</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>44574</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>45243</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40538,7 +40538,7 @@
         <v>44586</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>44491</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40684,7 +40684,7 @@
         <v>44911</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40757,7 +40757,7 @@
         <v>46119</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>46280</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>45317</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>44979</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45098</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41122,7 +41122,7 @@
         <v>46287</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41195,7 +41195,7 @@
         <v>46281</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>46289</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>46286</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44888</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41497,7 +41497,7 @@
         <v>46289</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>46289</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>46289</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>44978</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>46289</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>46289</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41955,7 +41955,7 @@
         <v>46289</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>45294</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42106,7 +42106,7 @@
         <v>45726</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>46293</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42257,7 +42257,7 @@
         <v>46167</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>45532</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>46290</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42476,7 +42476,7 @@
         <v>45166</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>44984</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>44943</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>44943</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42768,7 +42768,7 @@
         <v>44944</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42841,7 +42841,7 @@
         <v>45252</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42919,7 +42919,7 @@
         <v>46293</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>44495</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43070,7 +43070,7 @@
         <v>44914</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43143,7 +43143,7 @@
         <v>44974</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>46253</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43294,7 +43294,7 @@
         <v>46295</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>45173</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>45173</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>46295</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>44956</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>46252</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43752,7 +43752,7 @@
         <v>45747</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45344</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>46297</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>46296</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>44752</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>45693</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>46254</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>46296</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>46255</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>46255</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>45008</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44570,7 +44570,7 @@
         <v>46254</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>46255</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>46255</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>44602</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>46296</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44950,7 +44950,7 @@
         <v>46296</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>45050</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         <v>46254</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>44911</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>46296</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45330,7 +45330,7 @@
         <v>46255</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>46255</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>46255</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>44978</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>46253</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45705,7 +45705,7 @@
         <v>46255</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45778,7 +45778,7 @@
         <v>46296</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45856,7 +45856,7 @@
         <v>45743</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45929,7 +45929,7 @@
         <v>45664</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>45422</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46075,7 +46075,7 @@
         <v>45099</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45231</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>45511</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45058</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46372,7 +46372,7 @@
         <v>44993</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46445,7 +46445,7 @@
         <v>45572</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>44823</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46596,7 +46596,7 @@
         <v>44753</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45118</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46742,7 +46742,7 @@
         <v>45582</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46820,7 +46820,7 @@
         <v>44951</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46893,7 +46893,7 @@
         <v>45195</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>44916</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>44753</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>44613</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         <v>45075</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>44873</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47331,7 +47331,7 @@
         <v>45175</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47404,7 +47404,7 @@
         <v>45713</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>44981</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>45117</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47623,7 +47623,7 @@
         <v>45117</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47696,7 +47696,7 @@
         <v>45117</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47769,7 +47769,7 @@
         <v>45250</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47842,7 +47842,7 @@
         <v>44925</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>45727</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47988,7 +47988,7 @@
         <v>45103</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48061,7 +48061,7 @@
         <v>44620</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45747</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>45394</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48280,7 +48280,7 @@
         <v>44644</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>45355</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48426,7 +48426,7 @@
         <v>44629</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48499,7 +48499,7 @@
         <v>44546</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48577,7 +48577,7 @@
         <v>45191</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>44588</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48733,7 +48733,7 @@
         <v>44788</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48806,7 +48806,7 @@
         <v>44684</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48879,7 +48879,7 @@
         <v>45590</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48957,7 +48957,7 @@
         <v>45411</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49030,7 +49030,7 @@
         <v>45485</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>45699</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49186,7 +49186,7 @@
         <v>45411</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49259,7 +49259,7 @@
         <v>44788</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49332,7 +49332,7 @@
         <v>44629</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45987</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>46000</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49571,7 +49571,7 @@
         <v>46085</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>46190</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>46273</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>

--- a/Översikt HEBY.xlsx
+++ b/Översikt HEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45425</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45944</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45729</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45123</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45946</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>45618</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45777</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>46155</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45777</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>44914</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>44914</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>46149</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45117</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45687</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45985</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>46254</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>44585</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>44573</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>45124</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45222</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>45014</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>45485</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>44840</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>46070</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44788</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45112</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44847</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44524</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45618</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>45573</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>46163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>46217</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>46282</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45485</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45964</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45313</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45898</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>45419</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>45170</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>45944</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45278</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>45992</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>46140</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>46177</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>45460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45373</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>44847</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>44509</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44826</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45083</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>45093</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>45355</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>45883</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>45418</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>45117</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>45469</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>45411</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>45231</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>45278</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>45098</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>45050</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>45617</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45208</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45770</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44501</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>45622</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>45723</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>46140</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>45317</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>46070</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>46071</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>46084</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>46085</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>45972</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>46231</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>46295</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>46072</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44629</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45548</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>46107</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44756</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44886</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44620</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44754</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44615</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44516</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>44511</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44586</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44757</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>44585</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44508</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>44509</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>44756</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>44578</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>44480</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>44788</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44852</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44508</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>44505</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44517</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>44516</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44509</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>44565</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44735</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>44832</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44743</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44551</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44519</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>44844</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>44748</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>44712</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>44685</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44614</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>44850</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44769</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>44550</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>44491</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>44725</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>44832</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>44522</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44650</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>44655</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>44722</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>44700</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45231</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44573</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44753</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>45135</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>45132</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>45099</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45670</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>45390</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>45117</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>44944</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44917</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>44862</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>45607</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44568</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>45688</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>45250</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>45379</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>45279</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45599</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45344</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45321</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>45090</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>45308</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>44517</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44911</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>45103</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45761</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>44865</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45243</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44849</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>44823</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45331</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45250</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44543</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45551</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45519</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45519</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>44900</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44914</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>45342</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>45058</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45231</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45117</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>45117</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45117</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>44833</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45209</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45884</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45883</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>44552</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>44979</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>44978</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45713</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>44984</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>44984</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45321</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>44925</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>44875</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>44886</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>44531</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45339</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45502</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45006</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45889</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45029</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45891</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45898</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45898</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44844</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>44978</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45117</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>44568</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45740</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45175</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44574</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45439</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45098</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45617</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>44512</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44974</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45532</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45373</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>44913</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45747</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45075</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45726</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>45912</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45166</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>44993</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45511</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45106</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45294</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45092</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>44586</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45092</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44511</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45566</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45394</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>44903</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45117</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45589</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>44620</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44951</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45922</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44613</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44574</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>45355</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>45390</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45922</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>45922</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>45519</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44644</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45331</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>44558</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45119</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44945</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45173</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45173</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>45008</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>44873</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45567</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45175</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>44946</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45331</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45328</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45133</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45062</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45050</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44943</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44944</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44944</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>45112</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45209</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>45586</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>45610</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45337</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45181</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45599</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45797</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>44974</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45103</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>44943</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45727</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45747</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45547</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>44916</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>45930</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45674</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44802</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>44802</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>45804</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>45804</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>45364</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>45364</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45803</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>45166</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>45705</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>44623</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44888</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>45006</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>45390</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>45058</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45398</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45680</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>45050</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44609</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44984</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>44701</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45519</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45089</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45628</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45708</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45596</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45944</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45945</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>44601</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>45422</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>45195</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>44697</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45818</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45818</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>45195</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44491</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45133</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45092</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44697</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45113</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>44841</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>45820</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45138</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45950</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>44956</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44960</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45825</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45826</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>44694</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45952</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>45952</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>44984</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>44533</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44788</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28165,7 +28165,7 @@
         <v>45832</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>45951</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>45957</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>45958</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>45243</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>45764</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>45294</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>45764</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45250</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>44752</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>45838</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>45175</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>44791</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>45966</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45181</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>44802</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45967</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45845</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45971</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>45971</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45825</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>45749</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>45972</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29864,7 +29864,7 @@
         <v>44734</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         <v>45058</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>45847</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45852</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>45852</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45030</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>44810</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>45317</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>44984</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>44734</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45114</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>44754</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45132</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45132</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>44694</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45132</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44753</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>44609</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45098</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45980</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45743</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45980</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45980</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45118</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45351</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45293</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>45218</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45218</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45693</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>45777</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44781</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>46094</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>45216</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>45128</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>46101</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45197</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>44684</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>44732</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>44939</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45951</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>46110</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45895</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>45992</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45582</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>44914</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>46112</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>46112</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>46112</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>46112</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>46112</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>44538</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>46114</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>46114</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45406</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>46127</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>46126</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>46126</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>44911</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>44694</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44978</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>46133</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>46003</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>46003</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>44495</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>46005</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>45572</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>46003</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44659</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>46135</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>46135</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>46007</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>44614</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>45453</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>44942</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>44942</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>45664</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>44602</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>45113</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>44684</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>44522</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>44753</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
         <v>45895</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45006</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>44734</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45083</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>46023</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>44964</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>44701</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45013</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>44480</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45818</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45317</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45932</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>46140</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>46140</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>46140</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>44984</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>45215</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37108,7 +37108,7 @@
         <v>44984</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45411</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37254,7 +37254,7 @@
         <v>46140</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>45946</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44644</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45884</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>46140</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>45932</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>45035</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>45884</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45639</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>46044</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>44981</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>45891</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>45946</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45904</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>44914</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>46045</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>46048</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>45376</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>46140</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45252</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45111</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45805</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>46052</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>46052</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>46051</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>46052</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39187,7 +39187,7 @@
         <v>46084</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>46056</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>46058</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>46058</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>46057</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>46057</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>46058</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>46141</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>46059</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>46063</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>46063</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>46149</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>46071</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>46056</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>46073</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>46073</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>46076</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>46058</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>46079</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>45805</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45770</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>46160</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>46093</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>46093</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>46093</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>46164</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>46163</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>46168</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>46169</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>46037</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41397,7 +41397,7 @@
         <v>45967</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>46174</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41543,7 +41543,7 @@
         <v>46174</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>46178</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>46178</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>46198</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>46198</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45929</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>46205</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42069,7 +42069,7 @@
         <v>46205</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42147,7 +42147,7 @@
         <v>46220</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>46223</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>46265</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>46223</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>46224</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>46268</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>46268</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>46272</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>46272</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42839,7 +42839,7 @@
         <v>46272</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>46269</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>46231</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>46231</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>46273</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>46272</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>46237</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>46280</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43443,7 +43443,7 @@
         <v>46280</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>46280</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>46237</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>46237</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>46279</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>46278</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43896,7 +43896,7 @@
         <v>46279</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43969,7 +43969,7 @@
         <v>46281</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44042,7 +44042,7 @@
         <v>46238</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44120,7 +44120,7 @@
         <v>46238</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>46119</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>46286</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
         <v>46281</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>46287</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>46289</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44563,7 +44563,7 @@
         <v>46289</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>46290</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>46289</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>46289</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44870,7 +44870,7 @@
         <v>46289</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>46289</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>46289</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>46293</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>46167</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45245,7 +45245,7 @@
         <v>46293</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>46296</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>46296</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>46296</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>46295</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>46296</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45708,7 +45708,7 @@
         <v>46296</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>46252</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>46253</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>46254</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>46296</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>46253</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>46255</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>46255</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>46254</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>46255</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>46255</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>46255</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45317</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>46300</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>46255</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45786</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>46280</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>46254</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>46255</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47150,7 +47150,7 @@
         <v>46255</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47223,7 +47223,7 @@
         <v>46297</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>46301</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>46301</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>46302</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47515,7 +47515,7 @@
         <v>46301</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47588,7 +47588,7 @@
         <v>46258</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47661,7 +47661,7 @@
         <v>46258</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>46302</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>46258</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47880,7 +47880,7 @@
         <v>46301</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>46302</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>46302</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45827</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>46072</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>46303</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>46295</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45786</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>46262</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>44629</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>44546</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>44588</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>44684</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>44629</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45191</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>44788</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45590</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>45411</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45485</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45699</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49405,7 +49405,7 @@
         <v>45411</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>44788</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49551,7 +49551,7 @@
         <v>45987</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>46000</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>46085</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49775,7 +49775,7 @@
         <v>46190</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>46273</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>

--- a/Översikt HEBY.xlsx
+++ b/Översikt HEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45425</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45944</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45729</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45123</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45946</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>45618</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45777</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>46155</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45777</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>44914</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45240</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>44914</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>46149</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45117</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>45687</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45985</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>46254</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>44585</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>44573</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>45124</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45222</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>45014</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>45485</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>44840</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>46070</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44788</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45112</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44847</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>44524</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>45618</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>45573</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>46163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>46217</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>46282</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45485</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45964</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45313</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45898</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>45419</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>45170</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>45944</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45278</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>45992</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>46140</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>46177</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>45460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45373</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>44847</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>44509</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44826</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45083</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>45093</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>45355</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>45883</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>45418</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>45117</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>45469</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>45411</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>45231</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>45278</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         <v>45098</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>45050</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>45617</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45208</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45770</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>44501</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>45622</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>45723</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>46140</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>45317</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>46070</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>46071</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>46084</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>46085</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>45972</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>46231</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>46295</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>46072</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>44629</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>45548</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>46107</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44756</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>44886</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44620</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44754</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44615</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44516</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>44511</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44586</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44757</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>44585</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44508</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
         <v>44509</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>44756</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>44578</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>44480</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>44788</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>44852</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44508</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>44505</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>44517</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>44516</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44509</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11600,7 +11600,7 @@
         <v>44565</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44735</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>44832</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>44743</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44551</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44519</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>44844</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>44748</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>44712</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>44685</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44614</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>44850</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44769</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         <v>44550</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>44491</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>44725</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>44832</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>44522</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44650</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>44655</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>44722</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>44700</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45231</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>44573</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44753</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>44614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>45135</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>45132</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>45099</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13800,7 +13800,7 @@
         <v>45670</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>45390</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>45117</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>44944</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44917</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14165,7 +14165,7 @@
         <v>44862</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         <v>45607</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>44568</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>45688</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>45250</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>45379</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>45279</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45599</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45344</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45321</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>45090</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>45308</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>44517</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>44911</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>45103</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>45761</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>44865</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45243</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44849</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>44823</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45331</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45250</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44543</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45551</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45519</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>45519</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>44900</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44914</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>45342</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>45058</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45231</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45117</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>45117</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>45117</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>44833</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45209</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45884</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45883</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>44552</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>44979</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>44978</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45713</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>44984</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>44984</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>45321</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>44925</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>44875</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>44886</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>44531</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45339</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45502</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45006</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45889</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45029</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45891</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45898</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45898</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44844</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>44978</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45117</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>44568</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>45740</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45175</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>44574</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>45439</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45098</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>45617</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>44512</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>44974</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45532</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45373</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>44913</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45747</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45075</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45726</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>45912</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45166</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>44993</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45511</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45106</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45294</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45092</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>44586</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45092</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44511</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45566</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45394</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>44903</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45117</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>45589</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>44620</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>44951</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45922</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21009,7 +21009,7 @@
         <v>44613</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>44574</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21155,7 +21155,7 @@
         <v>45355</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>45390</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45922</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21374,7 +21374,7 @@
         <v>45922</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>45519</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44644</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45331</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>44558</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45119</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>44945</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45173</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45173</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>45008</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>44873</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45567</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45175</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>44946</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45331</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45328</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45133</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>45062</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45050</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44943</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>44944</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>44944</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22990,7 +22990,7 @@
         <v>45112</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23068,7 +23068,7 @@
         <v>45209</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23141,7 +23141,7 @@
         <v>45586</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23219,7 +23219,7 @@
         <v>45610</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23292,7 +23292,7 @@
         <v>45337</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45181</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>45599</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>45797</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>44974</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45103</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>44943</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45727</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45747</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45547</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>44916</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>45930</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24178,7 +24178,7 @@
         <v>45674</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24251,7 +24251,7 @@
         <v>44802</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>44802</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>45804</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>45804</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>45364</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>45364</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24689,7 +24689,7 @@
         <v>45803</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24762,7 +24762,7 @@
         <v>45166</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>45705</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>44623</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44888</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>45006</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25132,7 +25132,7 @@
         <v>45390</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>45058</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25283,7 +25283,7 @@
         <v>45398</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45680</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>45050</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44609</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>44984</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>44701</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25731,7 +25731,7 @@
         <v>45519</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25804,7 +25804,7 @@
         <v>45089</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45628</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45708</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>45596</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45944</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45945</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>44601</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>45422</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>45195</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26466,7 +26466,7 @@
         <v>44697</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26544,7 +26544,7 @@
         <v>45818</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>45818</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>45195</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44491</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26841,7 +26841,7 @@
         <v>45133</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26914,7 +26914,7 @@
         <v>45092</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26987,7 +26987,7 @@
         <v>44697</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45113</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>44841</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>45820</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45138</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45950</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>44956</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27508,7 +27508,7 @@
         <v>44960</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
         <v>45825</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45826</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         <v>44694</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27800,7 +27800,7 @@
         <v>45952</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>45952</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>44984</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         <v>44533</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>44788</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28165,7 +28165,7 @@
         <v>45832</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>45951</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28311,7 +28311,7 @@
         <v>45957</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28384,7 +28384,7 @@
         <v>45958</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>45243</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28530,7 +28530,7 @@
         <v>45764</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>45294</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>45764</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45250</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>44752</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>45838</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>45175</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>44791</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>45966</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45181</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>44802</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45967</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45845</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45971</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>45971</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45825</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>45749</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>45972</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29864,7 +29864,7 @@
         <v>44734</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         <v>45058</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>45847</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>45852</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>45852</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45030</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>44810</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>45317</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>44984</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>44734</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45114</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>44754</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>45132</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45132</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>44694</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45132</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44753</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>44609</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45098</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45980</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45743</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45980</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45980</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45118</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45351</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45293</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>45218</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45218</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45693</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>45777</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>44781</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>46094</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>45216</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>45128</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>46101</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45197</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>44684</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32590,7 +32590,7 @@
         <v>44732</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32663,7 +32663,7 @@
         <v>44939</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>45951</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32814,7 +32814,7 @@
         <v>46110</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32887,7 +32887,7 @@
         <v>45895</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32965,7 +32965,7 @@
         <v>45992</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45582</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>44914</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33189,7 +33189,7 @@
         <v>46112</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33262,7 +33262,7 @@
         <v>46112</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         <v>46112</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>46112</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>46112</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>44538</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33627,7 +33627,7 @@
         <v>46114</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33700,7 +33700,7 @@
         <v>46114</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45406</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>46127</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>46126</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>46126</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>44911</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>44694</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44978</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>46133</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>46003</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>46003</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>44495</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>46005</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>45572</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34732,7 +34732,7 @@
         <v>46003</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34805,7 +34805,7 @@
         <v>44659</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34878,7 +34878,7 @@
         <v>46135</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>46135</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>46007</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35107,7 +35107,7 @@
         <v>44614</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35180,7 +35180,7 @@
         <v>45453</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35253,7 +35253,7 @@
         <v>44942</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>44942</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>45664</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>44602</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>45113</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>44684</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>44522</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35769,7 +35769,7 @@
         <v>44753</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35842,7 +35842,7 @@
         <v>45895</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45006</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>44734</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45083</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>46023</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>44964</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>44701</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45013</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>44480</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45818</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45317</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>45932</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36728,7 +36728,7 @@
         <v>46140</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>46140</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>46140</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>44984</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>45215</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37108,7 +37108,7 @@
         <v>44984</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>45411</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37254,7 +37254,7 @@
         <v>46140</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>45946</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>44644</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45884</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>46140</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>45932</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37707,7 +37707,7 @@
         <v>45035</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>45884</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>45639</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>46044</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>44981</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38072,7 +38072,7 @@
         <v>45891</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38145,7 +38145,7 @@
         <v>45946</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>45904</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>44914</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38369,7 +38369,7 @@
         <v>46045</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>46048</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>45376</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>46140</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45252</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45111</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45805</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>46052</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>46052</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>46051</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>46052</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39187,7 +39187,7 @@
         <v>46084</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39260,7 +39260,7 @@
         <v>46056</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39333,7 +39333,7 @@
         <v>46058</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>46058</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>46057</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>46057</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>46058</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>46141</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>46059</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>46063</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>46063</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40000,7 +40000,7 @@
         <v>46149</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>46071</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>46056</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>46073</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>46073</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>46076</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>46058</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>46079</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>45805</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45770</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>46160</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>46093</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>46093</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>46093</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>46164</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41105,7 +41105,7 @@
         <v>46163</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>46168</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>46169</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>46037</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41397,7 +41397,7 @@
         <v>45967</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>46174</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41543,7 +41543,7 @@
         <v>46174</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41616,7 +41616,7 @@
         <v>46178</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>46178</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41762,7 +41762,7 @@
         <v>46198</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>46198</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>45929</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>46205</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42069,7 +42069,7 @@
         <v>46205</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42147,7 +42147,7 @@
         <v>46220</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>46223</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>46265</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>46223</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         <v>46224</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42532,7 +42532,7 @@
         <v>46268</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>46268</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42688,7 +42688,7 @@
         <v>46272</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>46272</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42839,7 +42839,7 @@
         <v>46272</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42917,7 +42917,7 @@
         <v>46269</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>46231</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43063,7 +43063,7 @@
         <v>46231</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43136,7 +43136,7 @@
         <v>46273</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43214,7 +43214,7 @@
         <v>46272</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>46237</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>46280</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43443,7 +43443,7 @@
         <v>46280</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>46280</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>46237</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>46237</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>46279</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43818,7 +43818,7 @@
         <v>46278</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43896,7 +43896,7 @@
         <v>46279</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43969,7 +43969,7 @@
         <v>46281</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44042,7 +44042,7 @@
         <v>46238</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44120,7 +44120,7 @@
         <v>46238</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>46119</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>46286</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
         <v>46281</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>46287</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>46289</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44563,7 +44563,7 @@
         <v>46289</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>46290</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>46289</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44792,7 +44792,7 @@
         <v>46289</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44870,7 +44870,7 @@
         <v>46289</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>46289</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>46289</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>46293</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45172,7 +45172,7 @@
         <v>46167</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45245,7 +45245,7 @@
         <v>46293</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45323,7 +45323,7 @@
         <v>46296</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>46296</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>46296</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>46295</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>46296</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45708,7 +45708,7 @@
         <v>46296</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45786,7 +45786,7 @@
         <v>46252</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>46253</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45942,7 +45942,7 @@
         <v>46254</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>46296</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>46253</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46171,7 +46171,7 @@
         <v>46255</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46244,7 +46244,7 @@
         <v>46255</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>46254</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46395,7 +46395,7 @@
         <v>46255</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46468,7 +46468,7 @@
         <v>46255</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>46255</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45317</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>46300</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>46255</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>45786</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>46280</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>46254</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>46255</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47150,7 +47150,7 @@
         <v>46255</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47223,7 +47223,7 @@
         <v>46297</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>46301</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>46301</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>46302</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47515,7 +47515,7 @@
         <v>46301</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47588,7 +47588,7 @@
         <v>46258</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47661,7 +47661,7 @@
         <v>46258</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47734,7 +47734,7 @@
         <v>46302</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>46258</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47880,7 +47880,7 @@
         <v>46301</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>46302</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>46302</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>45827</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>46072</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>46303</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>46295</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>45786</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>46262</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>44629</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>44546</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>44588</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>44684</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>44629</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45191</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>44788</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49098,7 +49098,7 @@
         <v>45590</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>45411</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45485</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45699</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49405,7 +49405,7 @@
         <v>45411</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>44788</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49551,7 +49551,7 @@
         <v>45987</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49624,7 +49624,7 @@
         <v>46000</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>46085</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49775,7 +49775,7 @@
         <v>46190</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>46273</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>

--- a/Översikt HEBY.xlsx
+++ b/Översikt HEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45425</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45944</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45729</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45123</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45946</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>45618</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45777</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>46155</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45777</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>44914</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>46302</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45240</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>46149</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>44914</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>46149</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>45687</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>45985</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>45117</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>46254</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44585</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>44573</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45014</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>46070</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>44840</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>45222</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>45485</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>45124</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44788</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45112</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>44847</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44524</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>45618</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>46163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>46217</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>46282</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>45573</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>45485</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>45964</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>45313</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
         <v>45898</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>45170</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46140</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45278</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45944</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>45992</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>46177</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>45419</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>45460</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45373</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44847</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44509</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>44826</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>45093</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>45770</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45883</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>45317</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45723</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>46140</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>45083</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>45622</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45418</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>45050</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>45617</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>46071</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>46070</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>46084</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>46085</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>44501</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>45972</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45098</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45355</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>45117</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>45469</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>45231</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>46231</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9222,7 +9222,7 @@
         <v>45208</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45278</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>46295</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>46072</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>45411</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>46309</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>45548</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44629</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>46107</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>44756</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>44886</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>44620</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44754</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>44615</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>44516</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>44511</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44585</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         <v>44586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44757</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44508</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>44509</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>44578</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44756</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>44788</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>44852</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>44508</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44505</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>44517</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>44516</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         <v>44565</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>44844</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44712</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>44550</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44832</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44509</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44735</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>44519</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44743</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>44614</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>44850</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44491</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>44725</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>44522</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>44832</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>44748</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>44551</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>44685</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44769</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>44650</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>44655</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>44722</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>44700</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>44532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>44573</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>44753</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>44614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>44841</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>45231</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>44942</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44609</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>44552</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>44802</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>45133</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44732</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>45599</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>44697</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>44849</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>45035</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>44865</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>45749</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>44960</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>45761</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>44844</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44914</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>44538</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>45688</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
         <v>45215</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>44543</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>44810</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44788</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>45331</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>44684</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>44684</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>45670</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>44734</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>44875</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>44522</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45111</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>44694</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44862</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45439</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44913</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>45293</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>45519</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>44984</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>45321</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>44574</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>45279</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>44886</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>45058</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>45453</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>44917</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44984</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45502</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45006</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>44609</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>44914</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>45218</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>45567</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>44781</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>44984</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>44984</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>44601</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44623</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>45777</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>45883</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>45932</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45317</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45339</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45331</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>45331</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45891</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>45617</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45884</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>44614</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45946</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45519</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45519</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45586</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>44701</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>45932</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>44984</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>45889</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>45818</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19487,7 +19487,7 @@
         <v>45119</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19565,7 +19565,7 @@
         <v>45946</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45132</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>45342</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>45891</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45411</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>45884</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20003,7 +20003,7 @@
         <v>45607</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45898</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45895</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>46140</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>46140</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45674</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>46141</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>46140</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>46140</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44533</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>45098</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>45805</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>46140</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>44754</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>46140</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>44697</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45912</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>44900</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>44701</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45294</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45106</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>45092</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>45092</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45006</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45308</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45922</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45922</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>45922</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>44833</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>44978</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>46149</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44568</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45113</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45805</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45930</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>44939</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45321</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>44734</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45364</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45770</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45944</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>45090</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>45945</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>45058</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>45390</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>45950</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45951</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>45952</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>45952</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45181</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>45957</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45351</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>45958</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45114</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45967</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>46160</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>45966</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>44694</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24312,7 +24312,7 @@
         <v>45209</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24385,7 +24385,7 @@
         <v>45971</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45971</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>45972</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45197</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>45175</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>45740</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24823,7 +24823,7 @@
         <v>46163</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>45980</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24969,7 +24969,7 @@
         <v>45980</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>45980</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>45218</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>45250</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>44531</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>44511</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>45895</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45951</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>45551</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>46164</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>45029</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>45992</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>45406</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>45599</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>46037</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>46169</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>44568</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45967</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>46168</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>46174</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>46003</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>46003</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>46003</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>46174</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>46005</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>46007</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>45128</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>44644</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>44942</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>45013</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>45092</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27252,7 +27252,7 @@
         <v>44659</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44694</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>46023</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>46178</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>46178</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27617,7 +27617,7 @@
         <v>45639</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         <v>45337</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45589</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>46045</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>46044</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>46048</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45181</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45062</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>46051</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45135</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>46052</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>46052</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>46084</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>46052</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>46056</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>46057</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>46057</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>45364</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>46058</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>46058</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>46059</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>46058</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>44512</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29316,7 +29316,7 @@
         <v>46063</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>46063</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29462,7 +29462,7 @@
         <v>44903</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>46056</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>46071</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>44802</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>44802</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>44734</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>46073</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>46073</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>44517</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>46076</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30197,7 +30197,7 @@
         <v>46058</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>44558</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>45250</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>46079</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45243</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>44791</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>44945</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>46094</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>46093</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>46093</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30927,7 +30927,7 @@
         <v>46093</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45117</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>44974</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>45113</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>45132</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31297,7 +31297,7 @@
         <v>45132</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31370,7 +31370,7 @@
         <v>45132</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>46101</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45050</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31594,7 +31594,7 @@
         <v>44944</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45566</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>46110</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>46198</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>46112</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>46112</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>46112</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>46112</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>46112</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>46198</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>46114</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>45030</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>46114</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>45006</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>45117</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>44964</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45195</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32845,7 +32845,7 @@
         <v>45929</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>46126</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32991,7 +32991,7 @@
         <v>46126</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33064,7 +33064,7 @@
         <v>45138</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33137,7 +33137,7 @@
         <v>46127</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33210,7 +33210,7 @@
         <v>46133</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33288,7 +33288,7 @@
         <v>46135</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>46135</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45166</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>45373</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45216</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>45904</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>45103</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33819,7 +33819,7 @@
         <v>45884</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>46205</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45376</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45083</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34116,7 +34116,7 @@
         <v>44944</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34189,7 +34189,7 @@
         <v>46205</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34267,7 +34267,7 @@
         <v>45379</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>44574</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45243</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>44586</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34559,7 +34559,7 @@
         <v>44491</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34632,7 +34632,7 @@
         <v>44911</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>45317</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>44979</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34851,7 +34851,7 @@
         <v>45098</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>46220</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35002,7 +35002,7 @@
         <v>46223</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>46223</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>44888</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35236,7 +35236,7 @@
         <v>46224</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>44978</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>46272</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>45294</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>46273</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>46272</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>46272</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45726</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>46272</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>45532</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45166</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36069,7 +36069,7 @@
         <v>44984</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36142,7 +36142,7 @@
         <v>44943</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36215,7 +36215,7 @@
         <v>44943</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>44944</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>45252</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>46231</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>46231</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>46279</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>46279</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>46278</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36809,7 +36809,7 @@
         <v>44495</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>44914</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>44974</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>45173</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>45173</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>46238</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>46237</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>46238</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>46237</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>46237</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>44956</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>45747</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>46280</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>46280</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>46280</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45344</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>46281</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>44752</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45693</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45008</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44602</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45050</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>44911</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>44978</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>45743</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>45664</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>45422</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38810,7 +38810,7 @@
         <v>45099</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38883,7 +38883,7 @@
         <v>45231</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45511</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39029,7 +39029,7 @@
         <v>45058</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>46119</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39180,7 +39180,7 @@
         <v>46287</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>44993</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39326,7 +39326,7 @@
         <v>46281</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>46289</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>46289</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>46289</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>46289</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>45572</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>44823</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>46289</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39935,7 +39935,7 @@
         <v>44753</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40008,7 +40008,7 @@
         <v>46289</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
         <v>46289</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45118</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>45582</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40310,7 +40310,7 @@
         <v>46293</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40388,7 +40388,7 @@
         <v>44951</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40461,7 +40461,7 @@
         <v>46167</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40534,7 +40534,7 @@
         <v>46290</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40607,7 +40607,7 @@
         <v>45195</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40680,7 +40680,7 @@
         <v>44916</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40753,7 +40753,7 @@
         <v>44753</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>46293</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>44613</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40977,7 +40977,7 @@
         <v>45075</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>44873</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>45175</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45713</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41269,7 +41269,7 @@
         <v>46253</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41347,7 +41347,7 @@
         <v>46295</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41425,7 +41425,7 @@
         <v>44981</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41498,7 +41498,7 @@
         <v>45117</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>46252</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45117</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>45117</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>45250</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>46297</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>44925</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>45727</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>46296</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45103</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
         <v>44620</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>46254</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>46296</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>46254</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42540,7 +42540,7 @@
         <v>46296</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>46296</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>46254</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>46296</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>46253</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42925,7 +42925,7 @@
         <v>46296</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>45317</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43076,7 +43076,7 @@
         <v>46255</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43149,7 +43149,7 @@
         <v>46300</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>46301</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43295,7 +43295,7 @@
         <v>46255</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45786</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43451,7 +43451,7 @@
         <v>46301</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43524,7 +43524,7 @@
         <v>46258</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43597,7 +43597,7 @@
         <v>45747</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>46255</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>46280</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43816,7 +43816,7 @@
         <v>46258</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43889,7 +43889,7 @@
         <v>46258</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43962,7 +43962,7 @@
         <v>46255</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>46301</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>46301</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44181,7 +44181,7 @@
         <v>46255</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>45394</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44332,7 +44332,7 @@
         <v>46255</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>46255</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>46255</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>44644</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44629,7 +44629,7 @@
         <v>45355</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44702,7 +44702,7 @@
         <v>45390</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>46302</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44848,7 +44848,7 @@
         <v>46295</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44926,7 +44926,7 @@
         <v>46302</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44999,7 +44999,7 @@
         <v>45786</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45077,7 +45077,7 @@
         <v>45827</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>46302</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>46307</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>44946</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45374,7 +45374,7 @@
         <v>45328</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45447,7 +45447,7 @@
         <v>45133</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45520,7 +45520,7 @@
         <v>45209</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>45898</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>45112</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>46072</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>45797</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45175</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45968,7 +45968,7 @@
         <v>46307</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46041,7 +46041,7 @@
         <v>45610</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46114,7 +46114,7 @@
         <v>45547</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46187,7 +46187,7 @@
         <v>46262</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>46303</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46333,7 +46333,7 @@
         <v>45803</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>46265</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>45705</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>45804</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>45804</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>46286</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46771,7 +46771,7 @@
         <v>45390</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>45708</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46917,7 +46917,7 @@
         <v>44984</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46990,7 +46990,7 @@
         <v>45628</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>45680</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>45596</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45398</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>45519</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47355,7 +47355,7 @@
         <v>46311</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>46311</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45089</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47574,7 +47574,7 @@
         <v>46311</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47647,7 +47647,7 @@
         <v>46311</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>46269</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47793,7 +47793,7 @@
         <v>45818</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45818</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>45820</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>46268</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48095,7 +48095,7 @@
         <v>45825</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48168,7 +48168,7 @@
         <v>46268</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48246,7 +48246,7 @@
         <v>45826</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         <v>45764</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48397,7 +48397,7 @@
         <v>45764</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45832</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45838</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45825</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45847</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48772,7 +48772,7 @@
         <v>45845</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48845,7 +48845,7 @@
         <v>45852</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>45852</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>44629</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49069,7 +49069,7 @@
         <v>44546</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45191</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>44588</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49303,7 +49303,7 @@
         <v>44788</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49376,7 +49376,7 @@
         <v>44684</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49449,7 +49449,7 @@
         <v>45590</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49527,7 +49527,7 @@
         <v>45411</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49600,7 +49600,7 @@
         <v>45485</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49678,7 +49678,7 @@
         <v>45699</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49756,7 +49756,7 @@
         <v>45411</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49829,7 +49829,7 @@
         <v>44788</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49902,7 +49902,7 @@
         <v>44629</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45987</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50068,7 +50068,7 @@
         <v>46000</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>46085</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50219,7 +50219,7 @@
         <v>46190</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>46273</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>

--- a/Översikt HEBY.xlsx
+++ b/Översikt HEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45425</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45944</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45729</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45123</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45946</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>45618</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45777</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>45777</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>46155</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>46302</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44914</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>46318</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>44914</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>45240</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>46149</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45117</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45985</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45687</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>46254</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>44585</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44573</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>45124</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>46070</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45014</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45485</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45222</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>44788</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>44524</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45573</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>46163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>45618</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>46217</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>46282</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>45485</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>45964</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>45898</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>45944</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>46177</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45313</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45992</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>45419</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>46314</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>46140</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>45170</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45278</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45460</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>45373</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44847</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44509</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44826</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>45083</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>45093</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>45972</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45418</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>46231</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>45411</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>46071</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>46295</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>46084</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>46085</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>45883</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>45723</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>46140</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>46309</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>45317</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>46072</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>45098</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>45355</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45117</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45469</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45231</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45278</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>45050</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45617</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>45208</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45770</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44501</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>45622</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>44629</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>45548</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>46107</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44756</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44886</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>44620</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44754</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>44615</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>44516</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>44511</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>44585</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>44757</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44508</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44509</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>44756</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>44578</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>44788</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>44852</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>44508</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>44505</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>44517</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>44516</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44565</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>44844</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44712</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>44550</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44832</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44509</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>44735</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>44743</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44519</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>44850</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44614</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>44725</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>44522</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44832</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>44748</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>44551</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>44685</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44769</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44650</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>44655</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>44722</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>44700</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>44532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>45572</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>44573</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44753</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>44614</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>44659</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>45688</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>45889</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>45379</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>44614</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>45453</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>44942</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44942</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>45891</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45331</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>45664</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44602</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45113</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45342</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44684</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>44522</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>45898</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44753</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>45006</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>45231</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>44734</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>45083</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44964</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44701</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>45013</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44984</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45912</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>45215</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>44984</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45106</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>45294</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>45092</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45092</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>46164</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>44644</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>46163</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>45922</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>45922</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>45922</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>45035</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>46168</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>46169</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>46037</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>45639</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>45967</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45390</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44981</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44914</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>46174</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45376</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45930</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>45252</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>45111</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>46174</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>45135</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>45250</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>45944</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45132</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>45117</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>45945</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>45308</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>44865</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45243</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44849</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>44823</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>45250</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45607</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>46178</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45950</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>46178</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45952</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45952</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45599</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45344</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45951</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45957</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45958</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44911</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>45551</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45519</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45519</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45231</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>44900</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45966</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45058</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44833</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>45967</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45209</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45971</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>45971</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>45972</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>46198</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>44979</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>46198</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45713</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45321</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45929</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45980</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>44875</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45980</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45980</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>46205</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>46205</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45951</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45895</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45117</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45992</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45740</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45175</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44978</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>44984</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44984</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45617</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>46220</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>45747</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>46223</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>44925</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>46224</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>46003</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>46003</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>46005</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>46003</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>46231</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>46231</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>46007</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>45394</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>46237</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>46280</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>46280</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>46280</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>46237</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>46237</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>46279</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>46278</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>46279</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45355</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>45390</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>44644</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>46281</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>46023</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>46238</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>46238</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>44886</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45175</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>46119</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44946</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>45328</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45133</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>45112</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45209</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45610</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45797</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>46044</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>46281</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>46045</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>46048</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>46287</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>45547</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>45804</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>45804</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>46052</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>46052</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>46051</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>45803</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>46052</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45705</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>46289</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>46289</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>46290</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>46084</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>46289</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>46056</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>46289</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>46289</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>45390</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45398</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>46058</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>45680</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>46058</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44984</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>46057</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>45519</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>46289</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>46057</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>45089</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>46058</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>46289</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>46059</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45628</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>45708</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>45596</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44531</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>45339</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>45502</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>46293</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>46063</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>46063</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45818</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>45818</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>46167</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>46293</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>46071</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>46056</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45820</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>46296</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>46296</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>46073</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>46073</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>46076</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>46296</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45825</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45826</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>46058</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>46079</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>46295</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>46296</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>46296</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>46252</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>46253</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>46254</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>46296</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>45832</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>46253</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>46255</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>46255</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>46254</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>46255</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>45764</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>45764</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>46255</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>46255</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45317</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30957,7 +30957,7 @@
         <v>45838</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>46300</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>46093</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>46255</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>46093</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>46093</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45786</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>46280</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>46254</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>46255</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>46094</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>46255</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>45845</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45825</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>46297</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>46101</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>46301</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>46301</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>45847</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>46302</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44844</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>46301</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>45852</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>45852</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>46258</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>44978</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>46258</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>46302</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>46258</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>46301</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>46110</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>46302</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>46112</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>46112</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>46112</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>46112</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>46112</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45827</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>46114</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>46114</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>46303</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45786</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44574</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45439</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>46127</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>46126</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>46126</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45898</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>46262</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>46133</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46307</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45777</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>44512</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>45884</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45883</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>44913</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45075</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>46135</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>46135</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>44586</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>46307</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>46265</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>45566</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>44903</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>46286</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45895</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>44574</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>46311</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>46311</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>46312</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>46314</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>46314</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>46311</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>46311</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>46268</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>46314</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>45818</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45317</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>45932</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>46140</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>46140</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>45519</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>46140</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>46312</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>46314</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>46314</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>46268</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>46314</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45411</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>46314</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>46140</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>45119</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>46314</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>45946</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45884</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>46140</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>46269</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>45932</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>44945</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>46272</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>46272</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>46273</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38553,7 +38553,7 @@
         <v>45884</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>46315</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38699,7 +38699,7 @@
         <v>44873</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>46315</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>46272</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>46272</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>45567</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39069,7 +39069,7 @@
         <v>46315</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>45891</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>45946</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>45904</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>46315</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45331</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>46072</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>45062</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>45050</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>44943</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>44944</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>44944</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>46140</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>46318</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>46318</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45586</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>44974</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>45805</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>46295</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>46318</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>46141</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44943</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>46318</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44916</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45364</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>45364</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>44888</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>45006</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>46149</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>45058</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>44701</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>45805</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>44601</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>45770</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>45422</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>44697</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41747,7 +41747,7 @@
         <v>45092</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45113</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>46160</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>44956</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>44960</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>44984</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44533</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>45294</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44802</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>45749</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42492,7 +42492,7 @@
         <v>45058</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45030</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>44810</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>44984</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42794,7 +42794,7 @@
         <v>45114</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42867,7 +42867,7 @@
         <v>44754</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>45132</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45132</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>44694</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45132</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>44609</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45098</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>45743</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45351</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43529,7 +43529,7 @@
         <v>45218</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>45218</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43675,7 +43675,7 @@
         <v>45216</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>44684</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43826,7 +43826,7 @@
         <v>44939</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43899,7 +43899,7 @@
         <v>44538</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>45099</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>45670</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44944</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>44917</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>44862</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>44568</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45279</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44483,7 +44483,7 @@
         <v>45321</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45090</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44634,7 +44634,7 @@
         <v>44517</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>45103</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45761</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>44543</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>44914</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>45117</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45117</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45117</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>44552</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45006</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45374,7 +45374,7 @@
         <v>45029</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45447,7 +45447,7 @@
         <v>44568</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45520,7 +45520,7 @@
         <v>45098</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>44974</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>45532</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>45373</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>45726</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>45166</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45958,7 +45958,7 @@
         <v>44993</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>45511</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>44511</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         <v>45117</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45589</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44620</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46396,7 +46396,7 @@
         <v>44951</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>44613</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>45331</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>44558</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46688,7 +46688,7 @@
         <v>45173</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45173</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46834,7 +46834,7 @@
         <v>45008</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>45337</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46980,7 +46980,7 @@
         <v>45181</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47053,7 +47053,7 @@
         <v>45599</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47131,7 +47131,7 @@
         <v>45103</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45727</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>45747</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>45674</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>44802</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47496,7 +47496,7 @@
         <v>44802</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47569,7 +47569,7 @@
         <v>45166</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>44623</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>45050</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47793,7 +47793,7 @@
         <v>44609</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45195</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47939,7 +47939,7 @@
         <v>45195</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48012,7 +48012,7 @@
         <v>45133</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>44697</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48158,7 +48158,7 @@
         <v>44841</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
         <v>45138</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>44694</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>44788</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45243</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45250</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48596,7 +48596,7 @@
         <v>44752</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45175</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48742,7 +48742,7 @@
         <v>44791</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48815,7 +48815,7 @@
         <v>45181</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48888,7 +48888,7 @@
         <v>44734</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>45317</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49034,7 +49034,7 @@
         <v>44734</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>44753</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45118</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49253,7 +49253,7 @@
         <v>45293</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45693</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>44781</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49472,7 +49472,7 @@
         <v>45128</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49545,7 +49545,7 @@
         <v>45197</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>44732</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45582</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>44914</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45406</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>44911</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>44694</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50066,7 +50066,7 @@
         <v>44978</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50139,7 +50139,7 @@
         <v>44495</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>44629</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50285,7 +50285,7 @@
         <v>44546</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>44588</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50441,7 +50441,7 @@
         <v>44684</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50514,7 +50514,7 @@
         <v>44629</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>45191</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50685,7 +50685,7 @@
         <v>44788</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>45590</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50836,7 +50836,7 @@
         <v>45411</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>45485</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45699</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51065,7 +51065,7 @@
         <v>45411</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51138,7 +51138,7 @@
         <v>44788</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45987</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>46000</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>46085</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>46190</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51513,7 +51513,7 @@
         <v>46273</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>

--- a/Översikt HEBY.xlsx
+++ b/Översikt HEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45425</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>45944</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45729</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45123</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>45944</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>45946</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>45618</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>45187</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>45777</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>45777</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>46155</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>46302</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44914</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>46318</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>44914</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>46149</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>45240</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>46149</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>45117</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45985</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>45687</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>46254</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>44585</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>44573</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>45124</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>46070</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45014</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         <v>45485</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45222</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>44788</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>44524</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>45573</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>46163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>45618</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>46217</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>46282</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>45485</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>45964</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>45898</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>45944</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>46177</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45313</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45992</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>45419</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>46314</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>46140</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>45170</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45278</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>45460</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>45373</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>44847</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44509</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44826</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>45083</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>45093</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>45972</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45418</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>46231</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>45411</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>46070</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>46071</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>46295</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>46084</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>46085</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>45883</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>45723</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         <v>46140</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>46309</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>45317</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>46072</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>45098</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>45355</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45117</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45469</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45231</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>45278</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>45050</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45617</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>45208</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>45770</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44501</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>45622</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>44629</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>45548</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>46107</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44756</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10383,7 +10383,7 @@
         <v>44886</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>44620</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44754</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>44615</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10675,7 +10675,7 @@
         <v>44516</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>44511</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44586</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>44585</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>44757</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>44508</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44509</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>44756</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>44578</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>44788</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>44852</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>44508</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>44505</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>44517</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>44516</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>44565</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>44844</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44712</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>44550</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44832</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44509</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>44735</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>44743</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44519</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>44850</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44614</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>44725</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>44522</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44832</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>44748</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>44551</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>44685</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44769</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44650</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>44655</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>44722</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>44700</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>44532</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>45572</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>44573</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44753</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>44614</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>44659</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>45688</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>45889</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>45379</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>44614</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>45453</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>44942</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>44942</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>45891</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45331</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>45664</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44602</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45113</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45342</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44684</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>44522</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>45898</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44753</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>45006</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>45231</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>44734</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>45083</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44964</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44701</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>45013</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44984</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45912</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>45215</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>44984</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45106</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>45294</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>45092</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45092</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>46164</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>44644</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>46163</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>45922</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>45922</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>45922</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>45035</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>46168</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>46169</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>46037</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>45639</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>45967</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>45390</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>44981</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>44914</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>46174</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45376</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45930</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>45252</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>45111</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>46174</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>45135</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>45250</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>45944</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>45132</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>45117</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>45945</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>45308</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18249,7 +18249,7 @@
         <v>44865</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45243</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>44849</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>44823</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>45250</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45607</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>46178</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45950</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>46178</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45952</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45952</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45599</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45344</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45951</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45957</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45958</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>44911</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>45551</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>45519</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>45519</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>45231</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>44900</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>45966</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45058</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>44833</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>45967</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45209</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45971</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>45971</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>45972</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>46198</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>44979</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20610,7 +20610,7 @@
         <v>46198</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45713</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45321</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45929</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45980</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>44875</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45980</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45980</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>46205</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>46205</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45951</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45895</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45117</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45992</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45740</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45175</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44978</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>44984</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44984</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>45617</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>46220</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22178,7 +22178,7 @@
         <v>45747</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22251,7 +22251,7 @@
         <v>46223</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>44925</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>46224</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>46003</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>46003</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>46005</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>46003</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>46231</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>46231</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>46007</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>45394</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>46237</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>46280</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>46280</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>46280</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>46237</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>46237</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>46279</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>46278</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>46279</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45355</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>45390</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>44644</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>46281</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>46023</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>46238</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>46238</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>44886</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45175</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>46119</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44946</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>45328</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45133</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>45112</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45209</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45610</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45797</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>46044</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>46281</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>46045</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>46048</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>46287</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25362,7 +25362,7 @@
         <v>45547</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         <v>45804</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25508,7 +25508,7 @@
         <v>45804</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>46052</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>46052</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25727,7 +25727,7 @@
         <v>46051</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>45803</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>46052</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45705</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>46289</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>46289</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>46290</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>46084</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>46289</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>46056</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>46289</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>46289</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>45390</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45398</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>46058</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>45680</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>46058</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>44984</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>46057</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>45519</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>46289</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>46057</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>45089</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>46058</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>46289</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>46059</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45628</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>45708</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>45596</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>44531</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>45339</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>45502</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28103,7 +28103,7 @@
         <v>46293</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>46063</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>46063</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45818</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>45818</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>46167</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>46293</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>46071</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>46056</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45820</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         <v>46296</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>46296</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>46073</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>46073</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>46076</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>46296</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45825</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45826</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>46058</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>46079</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>46295</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>46296</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>46296</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>46252</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>46253</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>46254</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30056,7 +30056,7 @@
         <v>46296</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>45832</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>46253</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>46255</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>46255</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>46254</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>46255</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>45764</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>45764</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         <v>46255</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>46255</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45317</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30957,7 +30957,7 @@
         <v>45838</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>46300</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>46093</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>46255</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         <v>46093</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>46093</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45786</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>46280</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>46254</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>46255</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>46094</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>46255</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>45845</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45825</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>46297</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>46101</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>46301</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>46301</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>45847</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>46302</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>44844</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>46301</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>45852</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>45852</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>46258</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>44978</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>46258</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>46302</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33031,7 +33031,7 @@
         <v>46258</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>46301</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>46110</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33250,7 +33250,7 @@
         <v>46302</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>46112</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>46112</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>46112</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>46112</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>46112</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45827</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33766,7 +33766,7 @@
         <v>46114</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>46114</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>46303</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45786</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34063,7 +34063,7 @@
         <v>44574</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34136,7 +34136,7 @@
         <v>45439</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>46127</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34282,7 +34282,7 @@
         <v>46126</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34355,7 +34355,7 @@
         <v>46126</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45898</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34501,7 +34501,7 @@
         <v>46262</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>46133</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>46307</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45777</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>44512</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34876,7 +34876,7 @@
         <v>45884</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34954,7 +34954,7 @@
         <v>45883</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>44913</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>45075</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>46135</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>46135</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>44586</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>46307</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>46265</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>45566</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>44903</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>46286</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45895</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>44574</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>46311</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>46311</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>46312</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>46314</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>46314</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>46311</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>46311</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>46268</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>46314</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>45818</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45317</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>45932</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>46140</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36882,7 +36882,7 @@
         <v>46140</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>45519</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>46140</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>46312</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>46314</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>46314</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>46268</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>46314</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45411</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>46314</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>46140</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>45119</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>46314</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>45946</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45884</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>46140</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>46269</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>45932</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>44945</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>46272</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>46272</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>46273</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38553,7 +38553,7 @@
         <v>45884</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38626,7 +38626,7 @@
         <v>46315</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38699,7 +38699,7 @@
         <v>44873</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>46315</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>46272</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>46272</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>45567</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39069,7 +39069,7 @@
         <v>46315</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>45891</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>45946</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>45904</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>46315</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>45331</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>46072</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>45062</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>45050</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>44943</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>44944</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>44944</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>46140</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>46318</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40106,7 +40106,7 @@
         <v>46318</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40179,7 +40179,7 @@
         <v>45586</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>44974</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>45805</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>46295</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>46318</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>46141</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44943</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>46318</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>44916</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45364</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>45364</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>44888</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>45006</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>46149</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41221,7 +41221,7 @@
         <v>45058</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>44701</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41377,7 +41377,7 @@
         <v>45805</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>44601</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>45770</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>45422</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>44697</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41747,7 +41747,7 @@
         <v>45092</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45113</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>46160</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>44956</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42049,7 +42049,7 @@
         <v>44960</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>44984</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>44533</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42268,7 +42268,7 @@
         <v>45294</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44802</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42419,7 +42419,7 @@
         <v>45749</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42492,7 +42492,7 @@
         <v>45058</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>45030</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>44810</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42721,7 +42721,7 @@
         <v>44984</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42794,7 +42794,7 @@
         <v>45114</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42867,7 +42867,7 @@
         <v>44754</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>45132</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45132</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>44694</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45132</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>44609</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45098</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>45743</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45351</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43529,7 +43529,7 @@
         <v>45218</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>45218</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43675,7 +43675,7 @@
         <v>45216</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>44684</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43826,7 +43826,7 @@
         <v>44939</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43899,7 +43899,7 @@
         <v>44538</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>45099</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>45670</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44118,7 +44118,7 @@
         <v>44944</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>44917</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>44862</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44337,7 +44337,7 @@
         <v>44568</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>45279</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44483,7 +44483,7 @@
         <v>45321</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44556,7 +44556,7 @@
         <v>45090</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44634,7 +44634,7 @@
         <v>44517</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>45103</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45761</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>44543</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>44914</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>45117</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45117</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>45117</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>44552</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45006</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45374,7 +45374,7 @@
         <v>45029</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45447,7 +45447,7 @@
         <v>44568</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45520,7 +45520,7 @@
         <v>45098</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>44974</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>45532</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>45373</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>45726</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>45166</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45958,7 +45958,7 @@
         <v>44993</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>45511</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46104,7 +46104,7 @@
         <v>44511</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         <v>45117</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>45589</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44620</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46396,7 +46396,7 @@
         <v>44951</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>44613</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>45331</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>44558</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46688,7 +46688,7 @@
         <v>45173</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45173</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46834,7 +46834,7 @@
         <v>45008</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>45337</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46980,7 +46980,7 @@
         <v>45181</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47053,7 +47053,7 @@
         <v>45599</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47131,7 +47131,7 @@
         <v>45103</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45727</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>45747</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>45674</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>44802</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47496,7 +47496,7 @@
         <v>44802</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47569,7 +47569,7 @@
         <v>45166</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>44623</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>45050</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47793,7 +47793,7 @@
         <v>44609</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45195</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47939,7 +47939,7 @@
         <v>45195</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48012,7 +48012,7 @@
         <v>45133</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>44697</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48158,7 +48158,7 @@
         <v>44841</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
         <v>45138</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>44694</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>44788</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45243</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         <v>45250</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48596,7 +48596,7 @@
         <v>44752</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45175</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48742,7 +48742,7 @@
         <v>44791</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48815,7 +48815,7 @@
         <v>45181</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48888,7 +48888,7 @@
         <v>44734</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48961,7 +48961,7 @@
         <v>45317</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49034,7 +49034,7 @@
         <v>44734</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>44753</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>45118</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49253,7 +49253,7 @@
         <v>45293</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49326,7 +49326,7 @@
         <v>45693</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>44781</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49472,7 +49472,7 @@
         <v>45128</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49545,7 +49545,7 @@
         <v>45197</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>44732</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>45582</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>44914</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45406</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>44911</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>44694</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50066,7 +50066,7 @@
         <v>44978</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50139,7 +50139,7 @@
         <v>44495</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>44629</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50285,7 +50285,7 @@
         <v>44546</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>44588</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50441,7 +50441,7 @@
         <v>44684</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50514,7 +50514,7 @@
         <v>44629</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50607,7 +50607,7 @@
         <v>45191</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50685,7 +50685,7 @@
         <v>44788</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>45590</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50836,7 +50836,7 @@
         <v>45411</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>45485</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50987,7 +50987,7 @@
         <v>45699</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51065,7 +51065,7 @@
         <v>45411</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51138,7 +51138,7 @@
         <v>44788</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>45987</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>46000</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>46085</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51435,7 +51435,7 @@
         <v>46190</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51513,7 +51513,7 @@
         <v>46273</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
